--- a/data/safety_corrective.xlsx
+++ b/data/safety_corrective.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,36 @@
   </si>
   <si>
     <t>Updated_At</t>
+  </si>
+  <si>
+    <t>50b65e3ef3d64c679ba3bb86b1ff2395</t>
+  </si>
+  <si>
+    <t>e070f48972f74c25a32e777cbcf38ea4</t>
+  </si>
+  <si>
+    <t>2eefcc0d5bfc4b5baf4c06f84e2a62e8</t>
+  </si>
+  <si>
+    <t>Update the work instruction manual</t>
+  </si>
+  <si>
+    <t>update work instructions</t>
+  </si>
+  <si>
+    <t>update xxxx</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>2025-12-02T20:12:21.386046</t>
+  </si>
+  <si>
+    <t>2025-12-03T13:34:24.750266</t>
+  </si>
+  <si>
+    <t>2025-12-03T17:50:36.523213</t>
   </si>
 </sst>
 </file>
@@ -395,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -424,6 +454,57 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
